--- a/api/templates/mtb_detected_rr_detected/fr.xlsx
+++ b/api/templates/mtb_detected_rr_detected/fr.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/mtb_detected_rr_detected/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4561A622-D147-0D49-BD12-494CF3558445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>MTB détecté, RR détecté</t>
+  </si>
+  <si>
+    <t>Plage de dates : &lt;Dates&gt;</t>
+  </si>
   <si>
     <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
   </si>
@@ -40,18 +40,45 @@
     <t>Patient ID</t>
   </si>
   <si>
+    <t>ID du patient 2</t>
+  </si>
+  <si>
+    <t>ID du cas</t>
+  </si>
+  <si>
+    <t>ID de l’échantillon</t>
+  </si>
+  <si>
+    <t>Âge</t>
+  </si>
+  <si>
+    <t>Appareil</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
     <t>Machine Id</t>
   </si>
   <si>
     <t>Test Date</t>
   </si>
   <si>
+    <t>Nom du dosage</t>
+  </si>
+  <si>
     <t>MTB</t>
   </si>
   <si>
     <t>RIF</t>
   </si>
   <si>
+    <t>Texte du résultat</t>
+  </si>
+  <si>
+    <t>Code d’erreur</t>
+  </si>
+  <si>
     <t>Test Notes</t>
   </si>
   <si>
@@ -76,6 +103,9 @@
     <t>&lt;deviceName&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;instrumentSerial&gt;</t>
   </si>
   <si>
@@ -98,49 +128,43 @@
   </si>
   <si>
     <t>&lt;notes&gt;</t>
-  </si>
-  <si>
-    <t>MTB détecté, RR détecté</t>
-  </si>
-  <si>
-    <t>Plage de dates : &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>ID du patient 2</t>
-  </si>
-  <si>
-    <t>ID du cas</t>
-  </si>
-  <si>
-    <t>ID de l’échantillon</t>
-  </si>
-  <si>
-    <t>Âge</t>
-  </si>
-  <si>
-    <t>Appareil</t>
-  </si>
-  <si>
-    <t>Nom du dosage</t>
-  </si>
-  <si>
-    <t>Texte du résultat</t>
-  </si>
-  <si>
-    <t>Code d’erreur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color theme="1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <family val="2"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -149,31 +173,14 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -199,72 +206,54 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -488,265 +477,275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="4" width="24.1640625" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="28" customWidth="1"/>
-    <col min="9" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="14.5" customWidth="1"/>
-    <col min="12" max="14" width="16.83203125" customWidth="1"/>
-    <col min="15" max="15" width="60.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="15" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" ht="21" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+    </row>
+    <row r="6" ht="16" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+    </row>
+    <row r="8" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" ht="31" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-    </row>
-    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="14" t="s">
+      <c r="G10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="H10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="I10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="J10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="K10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="14" t="s">
+      <c r="L10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="14" t="s">
+      <c r="M10" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O9" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
+      <c r="O10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="8:16" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="8:16" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/mtb_detected_rr_detected/fr.xlsx
+++ b/api/templates/mtb_detected_rr_detected/fr.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BB01BB-40CC-0747-AB7A-673104A920D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -133,54 +134,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -206,17 +211,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -477,15 +498,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="4" width="24.1640625" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="11" width="18.5" customWidth="1"/>
@@ -494,7 +515,7 @@
     <col min="16" max="16" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -513,7 +534,7 @@
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -532,7 +553,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -551,7 +572,7 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -570,7 +591,7 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -589,7 +610,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -605,7 +626,7 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -621,7 +642,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" ht="16" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
@@ -642,7 +663,7 @@
       <c r="N8" s="6"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" ht="31" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -692,7 +713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
@@ -742,10 +763,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="8:16" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="8:16" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>